--- a/NameTrace/public/samples/sample-roster.xlsx
+++ b/NameTrace/public/samples/sample-roster.xlsx
@@ -4,8 +4,6 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
-    <sheet name="Payroll" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -401,43 +399,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J33"/>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Full Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Leader at 12</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Leader at 144</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Leader at 1728</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Address</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Mobile Number</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Event Name</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Event Type</v>
+      </c>
+      <c r="J1" t="str">
+        <v>First Visit</v>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Full Name</v>
+        <v>Aisha Pillay</v>
       </c>
       <c r="B2" t="str">
-        <v>Leader at 12</v>
+        <v>Grace Mahlangu</v>
       </c>
       <c r="C2" t="str">
-        <v>Leader at 144</v>
+        <v>Peter Coetzee</v>
       </c>
       <c r="D2" t="str">
-        <v>Leader at 1728</v>
+        <v>Thabo Nkosi</v>
       </c>
       <c r="E2" t="str">
-        <v>Address</v>
+        <v>10 Jacaranda Street</v>
       </c>
       <c r="F2" t="str">
-        <v>Mobile Number</v>
+        <v>0820000100</v>
       </c>
       <c r="G2" t="str">
-        <v>Email</v>
+        <v>aisha@example.com</v>
       </c>
       <c r="H2" t="str">
-        <v>Event Name</v>
+        <v>Sunday service</v>
       </c>
       <c r="I2" t="str">
-        <v>Event Type</v>
-      </c>
-      <c r="J2" t="str">
-        <v>First Visit</v>
+        <v>Service</v>
+      </c>
+      <c r="J2" s="1">
+        <v>45300</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Aisha Pillay</v>
+        <v>Tariq Naidoo</v>
       </c>
       <c r="B3" t="str">
         <v>Grace Mahlangu</v>
@@ -446,16 +476,16 @@
         <v>Peter Coetzee</v>
       </c>
       <c r="D3" t="str">
-        <v>Sarah Connor</v>
+        <v>Thabo Nkosi</v>
       </c>
       <c r="E3" t="str">
-        <v>12 Oak Street</v>
+        <v>11 Jacaranda Street</v>
       </c>
       <c r="F3" t="str">
-        <v>0820000001</v>
+        <v>0820000101</v>
       </c>
       <c r="G3" t="str">
-        <v>aisha@example.com</v>
+        <v>tariq@example.com</v>
       </c>
       <c r="H3" t="str">
         <v>Youth night</v>
@@ -464,7 +494,7 @@
         <v>Youth</v>
       </c>
       <c r="J3" s="1">
-        <v>45301</v>
+        <v>45303</v>
       </c>
     </row>
     <row r="4">
@@ -478,30 +508,30 @@
         <v>Peter Coetzee</v>
       </c>
       <c r="D4" t="str">
-        <v>Sarah Conner</v>
+        <v>Thabo (TK) Nkosi</v>
       </c>
       <c r="E4" t="str">
-        <v>4 Elm Road</v>
+        <v>11 Jacaranda Street</v>
       </c>
       <c r="F4" t="str">
-        <v>0820000002</v>
+        <v>0820000101</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>tariq@example.com</v>
       </c>
       <c r="H4" t="str">
-        <v>Sunday service</v>
+        <v>Prayer evening</v>
       </c>
       <c r="I4" t="str">
-        <v>Service</v>
+        <v>Prayer</v>
       </c>
       <c r="J4" s="1">
-        <v>45308</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sarah Connor</v>
+        <v>Kyle Reese</v>
       </c>
       <c r="B5" t="str">
         <v>Grace Mahlangu</v>
@@ -513,27 +543,59 @@
         <v>Thabo Nkosi</v>
       </c>
       <c r="E5" t="str">
-        <v>9 Pine Avenue</v>
+        <v>12 Jacaranda Street</v>
       </c>
       <c r="F5" t="str">
-        <v>0820000003</v>
+        <v>0820000102</v>
       </c>
       <c r="G5" t="str">
-        <v>sconnor@example.com</v>
+        <v>kyle@example.com</v>
       </c>
       <c r="H5" t="str">
-        <v>Sunday service</v>
+        <v>Prayer evening</v>
       </c>
       <c r="I5" t="str">
-        <v>Service</v>
-      </c>
-      <c r="J5" t="str">
-        <v>2024/01/14</v>
+        <v>Prayer</v>
+      </c>
+      <c r="J5" s="1">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Kyle Reese</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Thabo Nkosi</v>
+      </c>
+      <c r="E6" t="str">
+        <v>12 Jacaranda Street</v>
+      </c>
+      <c r="F6" t="str">
+        <v>0820000102</v>
+      </c>
+      <c r="G6" t="str">
+        <v>kyle@example.com</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Varsity gathering</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Campus</v>
+      </c>
+      <c r="J6" s="1">
+        <v>45313</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Sipho Khumalo</v>
+        <v>Kyle Reese</v>
       </c>
       <c r="B7" t="str">
         <v>Grace Mahlangu</v>
@@ -545,81 +607,859 @@
         <v>Thabo Nkosi</v>
       </c>
       <c r="E7" t="str">
+        <v>12 Jacaranda Street</v>
+      </c>
+      <c r="F7" t="str">
+        <v>0820000102</v>
+      </c>
+      <c r="G7" t="str">
+        <v>kyle@example.com</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Sunday service</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Service</v>
+      </c>
+      <c r="J7" s="1">
+        <v>45320</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Lerato Dlamini</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Thabo Nkosi</v>
+      </c>
+      <c r="E8" t="str">
+        <v>13 Jacaranda Street</v>
+      </c>
+      <c r="F8" t="str">
+        <v>0820000103</v>
+      </c>
+      <c r="G8" t="str">
+        <v>lerato@example.com</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Varsity gathering</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Campus</v>
+      </c>
+      <c r="J8" s="1">
+        <v>45309</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Zanele Mokoena</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Thabo Nkosi</v>
+      </c>
+      <c r="E9" t="str">
+        <v>14 Jacaranda Street</v>
+      </c>
+      <c r="F9" t="str">
+        <v>0820000104</v>
+      </c>
+      <c r="G9" t="str">
+        <v>zanele@example.com</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Sunday service</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Service</v>
+      </c>
+      <c r="J9" s="1">
+        <v>45312</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Zanele Mokoena</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Thabo Nkosi</v>
+      </c>
+      <c r="E10" t="str">
+        <v>14 Jacaranda Street</v>
+      </c>
+      <c r="F10" t="str">
+        <v>0820000104</v>
+      </c>
+      <c r="G10" t="str">
+        <v>zanele@example.com</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Youth night</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Youth</v>
+      </c>
+      <c r="J10" s="1">
+        <v>45319</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Sipho Khumalo</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Megan Botha</v>
+      </c>
+      <c r="E11" t="str">
+        <v>15 Jacaranda Street</v>
+      </c>
+      <c r="F11" t="str">
+        <v>0820000105</v>
+      </c>
+      <c r="G11" t="str">
+        <v>sipho@example.com</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Youth night</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Youth</v>
+      </c>
+      <c r="J11" s="1">
+        <v>45315</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Sipho Khumalo</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Megan Botha</v>
+      </c>
+      <c r="E12" t="str">
+        <v>15 Jacaranda Street</v>
+      </c>
+      <c r="F12" t="str">
+        <v>0820000105</v>
+      </c>
+      <c r="G12" t="str">
+        <v>sipho@example.com</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Prayer evening</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Prayer</v>
+      </c>
+      <c r="J12" s="1">
+        <v>45322</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Sipho Khumalo</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Megan Botha</v>
+      </c>
+      <c r="E13" t="str">
+        <v>15 Jacaranda Street</v>
+      </c>
+      <c r="F13" t="str">
+        <v>0820000105</v>
+      </c>
+      <c r="G13" t="str">
+        <v>sipho@example.com</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Varsity gathering</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Campus</v>
+      </c>
+      <c r="J13" s="1">
+        <v>45329</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Refilwe Mahlangu</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Megan Botha</v>
+      </c>
+      <c r="E14" t="str">
+        <v>16 Jacaranda Street</v>
+      </c>
+      <c r="F14" t="str">
+        <v>0820000106</v>
+      </c>
+      <c r="G14" t="str">
+        <v>refilwe@example.com</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Prayer evening</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Prayer</v>
+      </c>
+      <c r="J14" s="1">
+        <v>45318</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>David van der Merwe</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Megan Botha</v>
+      </c>
+      <c r="E15" t="str">
+        <v>17 Jacaranda Street</v>
+      </c>
+      <c r="F15" t="str">
+        <v>0820000107</v>
+      </c>
+      <c r="G15" t="str">
+        <v>david@example.com</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Varsity gathering</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Campus</v>
+      </c>
+      <c r="J15" s="1">
+        <v>45321</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>David van der Merwe</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Megan Botha</v>
+      </c>
+      <c r="E16" t="str">
+        <v>17 Jacaranda Street</v>
+      </c>
+      <c r="F16" t="str">
+        <v>0820000107</v>
+      </c>
+      <c r="G16" t="str">
+        <v>david@example.com</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Sunday service</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Service</v>
+      </c>
+      <c r="J16" s="1">
+        <v>45328</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Nomsa Zulu</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Megan Botha</v>
+      </c>
+      <c r="E17" t="str">
+        <v>18 Jacaranda Street</v>
+      </c>
+      <c r="F17" t="str">
+        <v>0820000108</v>
+      </c>
+      <c r="G17" t="str">
+        <v>nomsa@example.com</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Sunday service</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Service</v>
+      </c>
+      <c r="J17" s="1">
+        <v>45324</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Nomsa Zulu</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Megan Botha</v>
+      </c>
+      <c r="E18" t="str">
+        <v>18 Jacaranda Street</v>
+      </c>
+      <c r="F18" t="str">
+        <v>0820000108</v>
+      </c>
+      <c r="G18" t="str">
+        <v>nomsa@example.com</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Youth night</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Youth</v>
+      </c>
+      <c r="J18" s="1">
+        <v>45331</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Nomsa Zulu</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Megan Botha</v>
+      </c>
+      <c r="E19" t="str">
+        <v>18 Jacaranda Street</v>
+      </c>
+      <c r="F19" t="str">
+        <v>0820000108</v>
+      </c>
+      <c r="G19" t="str">
+        <v>nomsa@example.com</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Prayer evening</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Prayer</v>
+      </c>
+      <c r="J19" s="1">
+        <v>45338</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>John Connor</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Sarah Connor</v>
+      </c>
+      <c r="E20" t="str">
+        <v>19 Jacaranda Street</v>
+      </c>
+      <c r="F20" t="str">
+        <v>0820000109</v>
+      </c>
+      <c r="G20" t="str">
+        <v>john@example.com</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Youth night</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Youth</v>
+      </c>
+      <c r="J20" s="1">
+        <v>45327</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Anna Petersen</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Sarah Connor</v>
+      </c>
+      <c r="E21" t="str">
+        <v>20 Jacaranda Street</v>
+      </c>
+      <c r="F21" t="str">
+        <v>0820000110</v>
+      </c>
+      <c r="G21" t="str">
+        <v>anna@example.com</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Prayer evening</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Prayer</v>
+      </c>
+      <c r="J21" s="1">
+        <v>45330</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Anna Petersen</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Sarah Connor</v>
+      </c>
+      <c r="E22" t="str">
+        <v>20 Jacaranda Street</v>
+      </c>
+      <c r="F22" t="str">
+        <v>0820000110</v>
+      </c>
+      <c r="G22" t="str">
+        <v>anna@example.com</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Varsity gathering</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Campus</v>
+      </c>
+      <c r="J22" s="1">
+        <v>45337</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Kagiso Molefe</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Sarah Connor</v>
+      </c>
+      <c r="E23" t="str">
+        <v>21 Jacaranda Street</v>
+      </c>
+      <c r="F23" t="str">
+        <v>0820000111</v>
+      </c>
+      <c r="G23" t="str">
+        <v>kagiso@example.com</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Varsity gathering</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Campus</v>
+      </c>
+      <c r="J23" s="1">
+        <v>45333</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Kagiso Molefe</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Sarah Connor</v>
+      </c>
+      <c r="E24" t="str">
+        <v>21 Jacaranda Street</v>
+      </c>
+      <c r="F24" t="str">
+        <v>0820000111</v>
+      </c>
+      <c r="G24" t="str">
+        <v>kagiso@example.com</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Sunday service</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Service</v>
+      </c>
+      <c r="J24" s="1">
+        <v>45340</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Kagiso Molefe</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Sarah Connor</v>
+      </c>
+      <c r="E25" t="str">
+        <v>21 Jacaranda Street</v>
+      </c>
+      <c r="F25" t="str">
+        <v>0820000111</v>
+      </c>
+      <c r="G25" t="str">
+        <v>kagiso@example.com</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Youth night</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Youth</v>
+      </c>
+      <c r="J25" s="1">
+        <v>45347</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Megan Adams</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Sarah Connor</v>
+      </c>
+      <c r="E26" t="str">
+        <v>22 Jacaranda Street</v>
+      </c>
+      <c r="F26" t="str">
+        <v>0820000112</v>
+      </c>
+      <c r="G26" t="str">
+        <v>megan@example.com</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Sunday service</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Service</v>
+      </c>
+      <c r="J26" s="1">
+        <v>45336</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Pieter de Wet</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Pieter Jacobs</v>
+      </c>
+      <c r="E27" t="str">
+        <v>23 Jacaranda Street</v>
+      </c>
+      <c r="F27" t="str">
+        <v>0820000113</v>
+      </c>
+      <c r="G27" t="str">
+        <v>pieter@example.com</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Youth night</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Youth</v>
+      </c>
+      <c r="J27" s="1">
+        <v>45339</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Pieter de Wet</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Pieter Jacobs</v>
+      </c>
+      <c r="E28" t="str">
+        <v>23 Jacaranda Street</v>
+      </c>
+      <c r="F28" t="str">
+        <v>0820000113</v>
+      </c>
+      <c r="G28" t="str">
+        <v>pieter@example.com</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Prayer evening</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Prayer</v>
+      </c>
+      <c r="J28" s="1">
+        <v>45346</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Thandi Ndlovu</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Pieter Jacobs</v>
+      </c>
+      <c r="E29" t="str">
+        <v>24 Jacaranda Street</v>
+      </c>
+      <c r="F29" t="str">
+        <v>0820000114</v>
+      </c>
+      <c r="G29" t="str">
+        <v>thandi@example.com</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Prayer evening</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Prayer</v>
+      </c>
+      <c r="J29" s="1">
+        <v>45342</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Thandi Ndlovu</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Pieter Jacobs</v>
+      </c>
+      <c r="E30" t="str">
+        <v>24 Jacaranda Street</v>
+      </c>
+      <c r="F30" t="str">
+        <v>0820000114</v>
+      </c>
+      <c r="G30" t="str">
+        <v>thandi@example.com</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Varsity gathering</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Campus</v>
+      </c>
+      <c r="J30" s="1">
+        <v>45349</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Thandi Ndlovu</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Pieter Jacobs</v>
+      </c>
+      <c r="E31" t="str">
+        <v>24 Jacaranda Street</v>
+      </c>
+      <c r="F31" t="str">
+        <v>0820000114</v>
+      </c>
+      <c r="G31" t="str">
+        <v>thandi@example.com</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Sunday service</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Service</v>
+      </c>
+      <c r="J31" s="1">
+        <v>45356</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>José Álvarez</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Pieter Jacobs</v>
+      </c>
+      <c r="E32" t="str">
+        <v>25 Jacaranda Street</v>
+      </c>
+      <c r="F32" t="str">
+        <v>0820000115</v>
+      </c>
+      <c r="G32" t="str">
+        <v>josé@example.com</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Varsity gathering</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Campus</v>
+      </c>
+      <c r="J32" s="1">
+        <v>45345</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Bongani Sithole</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Grace Mahlangu</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Peter Coetzee</v>
+      </c>
+      <c r="D33" t="str">
         <v/>
       </c>
-      <c r="F7" t="str">
-        <v>0820000004</v>
-      </c>
-      <c r="G7" t="str">
-        <v>sipho@example.com</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Youth night</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Youth</v>
-      </c>
-      <c r="J7" s="1">
-        <v>45322</v>
+      <c r="E33" t="str">
+        <v>3 Protea Road</v>
+      </c>
+      <c r="F33" t="str">
+        <v>0820000199</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>Sunday service</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Service</v>
+      </c>
+      <c r="J33" s="1">
+        <v>45340</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Employee</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Department</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Amount</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Connor, Sarah</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Outreach</v>
-      </c>
-      <c r="C2">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>David van der Merwe</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Finance</v>
-      </c>
-      <c r="C3">
-        <v>900</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J33"/>
   </ignoredErrors>
 </worksheet>
 </file>